--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE74429-746E-4142-8468-C5C47A4502BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483B555F-BD8B-4920-9DD5-183598757A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15558" uniqueCount="3757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15594" uniqueCount="3761">
   <si>
     <t>PDS No.</t>
   </si>
@@ -6485,7 +6485,7 @@
     <t>MP0291.3</t>
   </si>
   <si>
-    <t>Pet 180CC Micro Tablet Milky White 38mm 20gm Jar MPCI</t>
+    <t>Pet 180CC Micro Tablet Dark Milky White 38mm 20gm Jar MPCI</t>
   </si>
   <si>
     <t>MP0351</t>
@@ -11340,6 +11340,18 @@
   </si>
   <si>
     <t>Pet 60ml Round Dark Milky white 25mm 10.0gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0005.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet 30ml Round Dark Milky 25mm 7.5gm Bottle </t>
+  </si>
+  <si>
+    <t>MP0290.5</t>
+  </si>
+  <si>
+    <t>Pet 150CC Micro Tablet Dark Milky White 38mm 18gm Jar MPCI</t>
   </si>
 </sst>
 </file>
@@ -12111,30 +12123,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9B9BFD7-C55E-46DE-85EC-6B1622B321C2}" name="Table1" displayName="Table1" ref="A1:U838" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U838" xr:uid="{D9B9BFD7-C55E-46DE-85EC-6B1622B321C2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C43FDCD-A8A0-475A-85AC-0771C01ABB8B}" name="Table1" displayName="Table1" ref="A1:U840" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U840" xr:uid="{7C43FDCD-A8A0-475A-85AC-0771C01ABB8B}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{D34B1BBE-0AA4-41AF-846D-8F62CE7E4441}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{5772256A-B521-40CD-B3A8-139840CB89C7}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{7D29E0A0-3A3E-471A-88DE-859DA3019E27}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{759E212D-5D73-4DFA-A738-C66CE1A4AAAB}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{2D74E3BF-E3B4-427A-A770-85132BB8AB1E}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{E11247FA-6560-4A70-BA6A-4F33CE86EE4C}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{D36AA78B-1D24-43AA-BBB5-E1E3FC404D1C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{398CB402-8BA6-4414-9D63-430D66B1F8A1}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{47661555-DCD3-48E1-BE13-DEE1366557A8}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{FFEA18A4-F4AC-4B2A-A14B-2F943FA96A5F}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{59152D15-85F4-41D7-8CAB-41905F2A8972}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{D992B8C8-A4D2-471C-8B99-22EA743112E2}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{45955C21-5D62-4D9A-A94D-A46D6F56C835}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{65AB64C0-9CFB-421E-B609-82E961B268BA}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{8EA04DAE-75A7-4215-8744-B4C8EE32A9D4}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{D0B836C6-901C-4C94-B6A5-DD0CB354D2DE}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{F2931A6C-2180-417A-BE60-A350E8600806}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{4FBC82EF-CF68-485D-A125-40337C315F45}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{B28F63F6-C61E-4E3D-BB97-299E095EA87E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{8C4D1CDB-1E19-42C1-B447-815CC94E8F99}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{35F83CC5-1E37-421E-A100-CCA2D01EA9C0}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9ABD74D2-60A4-45FA-B9E1-1DC3D3FC1162}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{D31649FB-A39A-4DC2-B8F0-0E9F9F50259E}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{DCD1D749-63E7-43E4-9FDF-F496661DF21C}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{29E4C696-322C-48BC-9A11-4C80F1D70452}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{E9D1EC6B-5903-4A5A-B08F-BFFBA9357B6F}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{0964FF67-3D03-4ABB-B14E-6742756E2A36}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{D361B0A2-CF2D-4F4F-B268-BFE99F06C34E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{0F29183C-3B90-4F86-BE31-A72E614E42C3}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{2052805C-7D8C-4A39-9C5B-930482121A11}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{F6292997-E352-4CD3-AAEA-B7BA3B05C40F}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{C565C494-46FA-4357-9756-67093F458198}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{9702FD88-BE5A-44BA-B8C0-725F385AE32D}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{68B7B5DB-F6B4-42AA-A687-71F7AFA9D7D3}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{AEAEB8E6-946E-463E-BF49-0847E5D2AD3D}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{794D27C5-2224-47F9-96D6-DC51BDCFD64E}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{F37D464D-E1FF-43B4-8099-BBDBB7D1DA67}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B7478818-BC22-409C-8AF6-A8EF43E6721F}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{B78C90FC-4EC7-4CE1-AF16-769A264D6108}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{0B62566C-DA4A-466D-99E1-3819950AB122}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{8216F4C0-CE32-40D8-AB14-18ECA8FBF3D8}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{EB7B68F6-3E1B-4948-AD5B-5A9DA360FE46}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12437,7 +12449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U838"/>
+  <dimension ref="A1:U840"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64467,68 +64479,190 @@
       </c>
     </row>
     <row r="838" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A838" s="9">
+      <c r="A838" s="4">
         <v>837</v>
       </c>
-      <c r="B838" s="10"/>
-      <c r="C838" s="11" t="s">
+      <c r="B838" s="5"/>
+      <c r="C838" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="D838" s="10"/>
-      <c r="E838" s="11" t="s">
+      <c r="D838" s="5"/>
+      <c r="E838" s="6" t="s">
         <v>3755</v>
       </c>
-      <c r="F838" s="11" t="s">
+      <c r="F838" s="6" t="s">
         <v>3756</v>
       </c>
-      <c r="G838" s="11" t="s">
+      <c r="G838" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H838" s="11" t="s">
+      <c r="H838" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I838" s="11" t="s">
+      <c r="I838" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J838" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="K838" s="11" t="s">
+      <c r="K838" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L838" s="11" t="s">
+      <c r="L838" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="M838" s="11" t="s">
+      <c r="M838" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="N838" s="11" t="s">
+      <c r="N838" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O838" s="11" t="s">
+      <c r="O838" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="P838" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q838" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R838" s="11" t="s">
+      <c r="P838" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q838" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R838" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="S838" s="11" t="s">
+      <c r="S838" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="T838" s="11" t="s">
+      <c r="T838" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="U838" s="12" t="s">
+      <c r="U838" s="7" t="s">
         <v>389</v>
       </c>
     </row>
+    <row r="839" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A839" s="4">
+        <v>838</v>
+      </c>
+      <c r="B839" s="5"/>
+      <c r="C839" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D839" s="5"/>
+      <c r="E839" s="6" t="s">
+        <v>3757</v>
+      </c>
+      <c r="F839" s="6" t="s">
+        <v>3758</v>
+      </c>
+      <c r="G839" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H839" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="I839" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J839" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="K839" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L839" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M839" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N839" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O839" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P839" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q839" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R839" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="S839" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="T839" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="U839" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="840" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A840" s="9">
+        <v>839</v>
+      </c>
+      <c r="B840" s="10"/>
+      <c r="C840" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D840" s="10"/>
+      <c r="E840" s="11" t="s">
+        <v>3759</v>
+      </c>
+      <c r="F840" s="11" t="s">
+        <v>3760</v>
+      </c>
+      <c r="G840" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H840" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="I840" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="J840" s="13" t="s">
+        <v>2399</v>
+      </c>
+      <c r="K840" s="11" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L840" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="M840" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N840" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O840" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P840" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q840" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R840" s="11" t="s">
+        <v>2400</v>
+      </c>
+      <c r="S840" s="11" t="s">
+        <v>2401</v>
+      </c>
+      <c r="T840" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="U840" s="12" t="s">
+        <v>2402</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z0HWZPazZHHwTJBXKS9PcP/70vyj2n9Kx2c/V5XwaUYOeegdlquChduNo2raeFfNucRnZgNTfx5UaMhJSMDhQA==" saltValue="HRrCqjvNwSjHbyhmM0LICw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pvbdeGuIj8ZWpcf8M3WGBQpcCi9BN6UOrO3Grah5pNDm5ebltXuJo8J6TEuKNiBWbrqkpT21ughR6jHfJqlLZA==" saltValue="DZdz3U25Bya09Q7R3M8sBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANU\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67B0D35-1916-4636-A4ED-54AE09C1B0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8235"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15721" uniqueCount="3785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15793" uniqueCount="3814">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11424,12 +11425,100 @@
   </si>
   <si>
     <t>Pet 120CC ASB Tablet Clear 38mm 18gm Jar MPCI</t>
+  </si>
+  <si>
+    <t>MP0447</t>
+  </si>
+  <si>
+    <t>MP0447.1</t>
+  </si>
+  <si>
+    <t>Pet 1.5L Square Goli Clear 83mm 39gm Jar</t>
+  </si>
+  <si>
+    <t>Square Goli</t>
+  </si>
+  <si>
+    <t>110.00 ± 1.50</t>
+  </si>
+  <si>
+    <t>193.00 ± 1.50</t>
+  </si>
+  <si>
+    <t>39.00 ± 2.00</t>
+  </si>
+  <si>
+    <t>1550.00 ± 20.00</t>
+  </si>
+  <si>
+    <t>MP0470</t>
+  </si>
+  <si>
+    <t>MP0470.1</t>
+  </si>
+  <si>
+    <t>Pet 30ml JLI Clear Short Neck 19mm 5.5gm Bottle</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>19 Pcs x 15 Rows = 285 Pcs</t>
+  </si>
+  <si>
+    <t>26.80 ± 0.80</t>
+  </si>
+  <si>
+    <t>83.50 ± 0.80</t>
+  </si>
+  <si>
+    <t>5.50 ± 0.50</t>
+  </si>
+  <si>
+    <t>37.00 ± 3.00</t>
+  </si>
+  <si>
+    <t>MP0474</t>
+  </si>
+  <si>
+    <t>MP0474.1</t>
+  </si>
+  <si>
+    <t>Pet 1Kg Avon Clear 83mm 50gm Jar</t>
+  </si>
+  <si>
+    <t>MP0472</t>
+  </si>
+  <si>
+    <t>MP0472.1</t>
+  </si>
+  <si>
+    <t>Pet 30ml D Type Hair Oil Clear Short Neck 19mm 5.5gm Bottle</t>
+  </si>
+  <si>
+    <t>1967</t>
+  </si>
+  <si>
+    <t>26 Pcs x 6 Rows = 156 Pcs
+25 Pcs x 5 Rows = 125 Pcs</t>
+  </si>
+  <si>
+    <t>D Type Hair Oil</t>
+  </si>
+  <si>
+    <t>39.00 ± 0.80</t>
+  </si>
+  <si>
+    <t>86.30 ± 0.80</t>
+  </si>
+  <si>
+    <t>36.00 ± 3.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -11580,34 +11669,34 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -11629,9 +11718,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -11651,21 +11740,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11688,21 +11762,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11727,21 +11786,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11766,21 +11810,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11805,21 +11834,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11844,21 +11858,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11883,21 +11882,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11922,21 +11906,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11961,21 +11930,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12000,21 +11954,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12039,21 +11978,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12078,21 +12002,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12117,21 +12026,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12156,21 +12050,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12195,21 +12074,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12234,21 +12098,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12273,21 +12122,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12334,21 +12168,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12395,22 +12214,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -12462,21 +12265,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -12493,30 +12281,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U847" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U847"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F78E430-41F2-4680-87E2-1DA43149C2EF}" name="Table1" displayName="Table1" ref="A1:U851" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U851" xr:uid="{4F78E430-41F2-4680-87E2-1DA43149C2EF}"/>
   <tableColumns count="21">
-    <tableColumn id="1" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C94CDFE6-1572-48BA-8611-4148DE81780C}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{CDC7F929-9E7B-4913-8B2B-A5039997E971}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{B833F614-03B7-423C-925C-7C689DC86889}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{7E89702C-C623-49A5-B855-E65A7832CA71}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{F8389D86-9C16-4351-B317-861FF9C59A76}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{78F583A9-8E8D-4EA7-81C0-61F677859149}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E3D5AEDD-7490-4C45-BD18-C0E0B84A3D41}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{8CD34757-3054-4773-88C0-6B1FE0C7E4DA}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{CEF2A571-C839-46E9-A017-CC0FB3EF6624}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{88EDE30A-6EA3-44DF-8F45-6EAC8EB63BB1}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{D753DA82-4DA9-4AF1-9A1E-FDAF669B4A8B}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{66E93494-95C8-40B2-9923-203F258FBE8C}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{9ED384CA-DA95-4FFE-857E-BD669BD8321A}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{3B87FF7B-FF95-4FBC-BBDA-7E13C300CFA8}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{DBE5BADF-F1D7-4A53-BB5F-619016177B85}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{69BE9812-970C-4AA1-87E3-746EC60520B3}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{D4D1EB15-D5DA-471C-A344-BCDD1B2FC495}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{93D66D13-2006-497C-A48E-2E99C44488C4}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{8D83D4E6-6CD2-45A1-B158-20CE96F304F0}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{6A941A8B-E1CF-439C-A856-722D6B3EB4AF}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{A3B8E923-4F2C-4CD7-8B35-33632E49993B}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12539,7 +12327,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -12551,7 +12339,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -12568,9 +12356,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -12598,14 +12386,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -12633,6 +12438,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -12784,8 +12606,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U847"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U851"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -65366,68 +65188,312 @@
       </c>
     </row>
     <row r="847" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A847" s="9">
+      <c r="A847" s="4">
         <v>846</v>
       </c>
-      <c r="B847" s="10"/>
-      <c r="C847" s="11" t="s">
+      <c r="B847" s="5"/>
+      <c r="C847" s="6" t="s">
         <v>3261</v>
       </c>
-      <c r="D847" s="10"/>
-      <c r="E847" s="11" t="s">
+      <c r="D847" s="5"/>
+      <c r="E847" s="6" t="s">
         <v>3783</v>
       </c>
-      <c r="F847" s="11" t="s">
+      <c r="F847" s="6" t="s">
         <v>3784</v>
       </c>
-      <c r="G847" s="11" t="s">
+      <c r="G847" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H847" s="11" t="s">
+      <c r="H847" s="6" t="s">
         <v>3059</v>
       </c>
-      <c r="I847" s="11" t="s">
+      <c r="I847" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J847" s="11" t="s">
+      <c r="J847" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="K847" s="11" t="s">
+      <c r="K847" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="L847" s="11" t="s">
+      <c r="L847" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="M847" s="11" t="s">
+      <c r="M847" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="N847" s="11" t="s">
+      <c r="N847" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O847" s="11" t="s">
+      <c r="O847" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P847" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q847" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R847" s="11" t="s">
+      <c r="P847" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q847" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R847" s="6" t="s">
         <v>3264</v>
       </c>
-      <c r="S847" s="11" t="s">
+      <c r="S847" s="6" t="s">
         <v>3265</v>
       </c>
-      <c r="T847" s="11" t="s">
+      <c r="T847" s="6" t="s">
         <v>858</v>
       </c>
-      <c r="U847" s="12" t="s">
+      <c r="U847" s="7" t="s">
         <v>3266</v>
       </c>
     </row>
+    <row r="848" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A848" s="4">
+        <v>847</v>
+      </c>
+      <c r="B848" s="5"/>
+      <c r="C848" s="6" t="s">
+        <v>3785</v>
+      </c>
+      <c r="D848" s="5"/>
+      <c r="E848" s="6" t="s">
+        <v>3786</v>
+      </c>
+      <c r="F848" s="6" t="s">
+        <v>3787</v>
+      </c>
+      <c r="G848" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H848" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="I848" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J848" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="K848" s="6" t="s">
+        <v>3788</v>
+      </c>
+      <c r="L848" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M848" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N848" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O848" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P848" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q848" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="R848" s="6" t="s">
+        <v>3789</v>
+      </c>
+      <c r="S848" s="6" t="s">
+        <v>3790</v>
+      </c>
+      <c r="T848" s="6" t="s">
+        <v>3791</v>
+      </c>
+      <c r="U848" s="7" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="849" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A849" s="4">
+        <v>848</v>
+      </c>
+      <c r="B849" s="5"/>
+      <c r="C849" s="6" t="s">
+        <v>3793</v>
+      </c>
+      <c r="D849" s="5"/>
+      <c r="E849" s="6" t="s">
+        <v>3794</v>
+      </c>
+      <c r="F849" s="6" t="s">
+        <v>3795</v>
+      </c>
+      <c r="G849" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H849" s="6" t="s">
+        <v>3796</v>
+      </c>
+      <c r="I849" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J849" s="6" t="s">
+        <v>3797</v>
+      </c>
+      <c r="K849" s="6" t="s">
+        <v>2288</v>
+      </c>
+      <c r="L849" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M849" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N849" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O849" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P849" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q849" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R849" s="6" t="s">
+        <v>3798</v>
+      </c>
+      <c r="S849" s="6" t="s">
+        <v>3799</v>
+      </c>
+      <c r="T849" s="6" t="s">
+        <v>3800</v>
+      </c>
+      <c r="U849" s="7" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="850" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A850" s="4">
+        <v>849</v>
+      </c>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6" t="s">
+        <v>3802</v>
+      </c>
+      <c r="D850" s="5"/>
+      <c r="E850" s="6" t="s">
+        <v>3803</v>
+      </c>
+      <c r="F850" s="6" t="s">
+        <v>3804</v>
+      </c>
+      <c r="G850" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H850" s="6" t="s">
+        <v>3749</v>
+      </c>
+      <c r="I850" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J850" s="6" t="s">
+        <v>3750</v>
+      </c>
+      <c r="K850" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L850" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M850" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N850" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O850" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P850" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q850" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="R850" s="6" t="s">
+        <v>3751</v>
+      </c>
+      <c r="S850" s="6" t="s">
+        <v>3752</v>
+      </c>
+      <c r="T850" s="6" t="s">
+        <v>2597</v>
+      </c>
+      <c r="U850" s="7" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="851" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A851" s="9">
+        <v>850</v>
+      </c>
+      <c r="B851" s="10"/>
+      <c r="C851" s="11" t="s">
+        <v>3805</v>
+      </c>
+      <c r="D851" s="10"/>
+      <c r="E851" s="11" t="s">
+        <v>3806</v>
+      </c>
+      <c r="F851" s="11" t="s">
+        <v>3807</v>
+      </c>
+      <c r="G851" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H851" s="11" t="s">
+        <v>3808</v>
+      </c>
+      <c r="I851" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J851" s="11" t="s">
+        <v>3809</v>
+      </c>
+      <c r="K851" s="11" t="s">
+        <v>3810</v>
+      </c>
+      <c r="L851" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M851" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N851" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O851" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P851" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q851" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R851" s="11" t="s">
+        <v>3811</v>
+      </c>
+      <c r="S851" s="11" t="s">
+        <v>3812</v>
+      </c>
+      <c r="T851" s="11" t="s">
+        <v>3800</v>
+      </c>
+      <c r="U851" s="12" t="s">
+        <v>3813</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1gRCGAYD3rC0rM4U0u+pLfJKkMhz0LxQRdDpOY+8ZPvAf8r9RvFtE+FMNPxBwzBX+kuox6RlfdG+xwAiYavriw==" saltValue="ekwHNzdiAZ8PtNHeFV8DSA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Dzhl23rTgykvy0kO6O1C6nLJNaL/lxCUY5BKfhiu70dC0nMpPpkFlxi8epj3CqpLqVKN+ZE/kDe5fFpY5HTHrA==" saltValue="SGkv3rW06GS2mHKNp0heyg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67B0D35-1916-4636-A4ED-54AE09C1B0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D16E2BC-EBD8-4C9F-B721-516B8A4822A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15793" uniqueCount="3814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15817" uniqueCount="3818">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11243,10 +11243,7 @@
     <t>Pet 200gm Powder Clear 63mm 21gm Jar</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Pending Matrix</t>
+    <t>405</t>
   </si>
   <si>
     <t>Powder</t>
@@ -11513,6 +11510,21 @@
   </si>
   <si>
     <t>36.00 ± 3.00</t>
+  </si>
+  <si>
+    <t>MP0451</t>
+  </si>
+  <si>
+    <t>MP0451.1</t>
+  </si>
+  <si>
+    <t>Pet 150CC ASB Tablet Amber 38mm 20gm Jar MPCI</t>
+  </si>
+  <si>
+    <t>105.50 ± 1.20</t>
+  </si>
+  <si>
+    <t>170.00 ± 5.00</t>
   </si>
 </sst>
 </file>
@@ -12281,30 +12293,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F78E430-41F2-4680-87E2-1DA43149C2EF}" name="Table1" displayName="Table1" ref="A1:U851" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U851" xr:uid="{4F78E430-41F2-4680-87E2-1DA43149C2EF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}" name="Table1" displayName="Table1" ref="A1:U852" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U852" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C94CDFE6-1572-48BA-8611-4148DE81780C}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{CDC7F929-9E7B-4913-8B2B-A5039997E971}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{B833F614-03B7-423C-925C-7C689DC86889}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{7E89702C-C623-49A5-B855-E65A7832CA71}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{F8389D86-9C16-4351-B317-861FF9C59A76}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{78F583A9-8E8D-4EA7-81C0-61F677859149}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{E3D5AEDD-7490-4C45-BD18-C0E0B84A3D41}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{8CD34757-3054-4773-88C0-6B1FE0C7E4DA}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{CEF2A571-C839-46E9-A017-CC0FB3EF6624}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{88EDE30A-6EA3-44DF-8F45-6EAC8EB63BB1}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{D753DA82-4DA9-4AF1-9A1E-FDAF669B4A8B}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{66E93494-95C8-40B2-9923-203F258FBE8C}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{9ED384CA-DA95-4FFE-857E-BD669BD8321A}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{3B87FF7B-FF95-4FBC-BBDA-7E13C300CFA8}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{DBE5BADF-F1D7-4A53-BB5F-619016177B85}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{69BE9812-970C-4AA1-87E3-746EC60520B3}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{D4D1EB15-D5DA-471C-A344-BCDD1B2FC495}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{93D66D13-2006-497C-A48E-2E99C44488C4}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{8D83D4E6-6CD2-45A1-B158-20CE96F304F0}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{6A941A8B-E1CF-439C-A856-722D6B3EB4AF}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{A3B8E923-4F2C-4CD7-8B35-33632E49993B}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0E466952-5BCD-4DBD-B7E0-94B822111115}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{94CFF99D-BDC8-46BB-8611-2C58783F62D6}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{48812F9D-3F1D-4BB0-B488-442FBFCB643B}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{16F470E3-FF94-4826-B6AF-3D9096C54514}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{7F5CFA63-21FA-4D5A-A7DC-86D63DD06FC2}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{D04041CE-09A9-4AB8-9986-FD0B72D39061}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{B088E793-5D8E-47C3-B17E-8976FE184B2C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B96EF495-338D-4355-9634-0DF56864B888}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{C0FDA1BC-B48D-48F5-9AFC-D50E079A2E17}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{5CAC9926-9171-4E60-8CD4-0A90E97E9440}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{CBD6D1A9-3D03-4D22-BC07-341610ABD5D2}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{42301E5C-ACCE-4E7F-A954-C672328B140F}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{87E1B73B-2D74-46B2-96C4-D3FCAA80D516}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{DD2E8F3F-1FC5-4E33-AD54-96B1C0F4EEC9}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{2F3F91F5-A260-4EBE-B03C-A7A87C1E2426}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{9DAECD21-9A7C-471D-89C4-BE7110C2F7BE}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{BE9BBD67-6EB6-43A1-AD65-17EC8AAB6BCD}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{64F8EDE7-2095-40C0-A74E-9AE1A5A5E0FF}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{0B8903B1-A8D4-4690-BD66-E33246B810C8}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{A3215038-E5B2-4B76-BFCD-E2001696F644}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{2F65A95A-4221-48C5-BD00-1D63995D82FA}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12607,7 +12619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U851"/>
+  <dimension ref="A1:U852"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64298,37 +64310,49 @@
         <v>3723</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="H832" s="6" t="s">
         <v>3724</v>
       </c>
       <c r="I832" s="6" t="s">
-        <v>3724</v>
+        <v>61</v>
       </c>
       <c r="J832" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K832" s="6" t="s">
         <v>3725</v>
       </c>
-      <c r="K832" s="6" t="s">
+      <c r="L832" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M832" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N832" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O832" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P832" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q832" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R832" s="6" t="s">
         <v>3726</v>
       </c>
-      <c r="L832" s="5"/>
-      <c r="M832" s="5"/>
-      <c r="N832" s="5"/>
-      <c r="O832" s="5"/>
-      <c r="P832" s="5"/>
-      <c r="Q832" s="5"/>
-      <c r="R832" s="6" t="s">
+      <c r="S832" s="6" t="s">
         <v>3727</v>
       </c>
-      <c r="S832" s="6" t="s">
+      <c r="T832" s="6" t="s">
         <v>3728</v>
       </c>
-      <c r="T832" s="6" t="s">
+      <c r="U832" s="7" t="s">
         <v>3729</v>
-      </c>
-      <c r="U832" s="7" t="s">
-        <v>3730</v>
       </c>
     </row>
     <row r="833" spans="1:21" x14ac:dyDescent="0.2">
@@ -64343,10 +64367,10 @@
       </c>
       <c r="D833" s="5"/>
       <c r="E833" s="6" t="s">
+        <v>3730</v>
+      </c>
+      <c r="F833" s="6" t="s">
         <v>3731</v>
-      </c>
-      <c r="F833" s="6" t="s">
-        <v>3732</v>
       </c>
       <c r="G833" s="6" t="s">
         <v>25</v>
@@ -64400,14 +64424,14 @@
       </c>
       <c r="B834" s="5"/>
       <c r="C834" s="6" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="D834" s="5"/>
       <c r="E834" s="6" t="s">
+        <v>3733</v>
+      </c>
+      <c r="F834" s="6" t="s">
         <v>3734</v>
-      </c>
-      <c r="F834" s="6" t="s">
-        <v>3735</v>
       </c>
       <c r="G834" s="6" t="s">
         <v>25</v>
@@ -64461,14 +64485,14 @@
       </c>
       <c r="B835" s="5"/>
       <c r="C835" s="6" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="D835" s="5"/>
       <c r="E835" s="6" t="s">
+        <v>3736</v>
+      </c>
+      <c r="F835" s="6" t="s">
         <v>3737</v>
-      </c>
-      <c r="F835" s="6" t="s">
-        <v>3738</v>
       </c>
       <c r="G835" s="6" t="s">
         <v>25</v>
@@ -64480,10 +64504,10 @@
         <v>146</v>
       </c>
       <c r="J835" s="6" t="s">
+        <v>3738</v>
+      </c>
+      <c r="K835" s="6" t="s">
         <v>3739</v>
-      </c>
-      <c r="K835" s="6" t="s">
-        <v>3740</v>
       </c>
       <c r="L835" s="6" t="s">
         <v>258</v>
@@ -64504,16 +64528,16 @@
         <v>35</v>
       </c>
       <c r="R835" s="6" t="s">
+        <v>3740</v>
+      </c>
+      <c r="S835" s="6" t="s">
         <v>3741</v>
-      </c>
-      <c r="S835" s="6" t="s">
-        <v>3742</v>
       </c>
       <c r="T835" s="6" t="s">
         <v>2316</v>
       </c>
       <c r="U835" s="7" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="836" spans="1:21" x14ac:dyDescent="0.2">
@@ -64526,10 +64550,10 @@
       </c>
       <c r="D836" s="5"/>
       <c r="E836" s="6" t="s">
+        <v>3743</v>
+      </c>
+      <c r="F836" s="6" t="s">
         <v>3744</v>
-      </c>
-      <c r="F836" s="6" t="s">
-        <v>3745</v>
       </c>
       <c r="G836" s="6" t="s">
         <v>239</v>
@@ -64583,26 +64607,26 @@
       </c>
       <c r="B837" s="5"/>
       <c r="C837" s="6" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="D837" s="5"/>
       <c r="E837" s="6" t="s">
+        <v>3746</v>
+      </c>
+      <c r="F837" s="6" t="s">
         <v>3747</v>
-      </c>
-      <c r="F837" s="6" t="s">
-        <v>3748</v>
       </c>
       <c r="G837" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H837" s="6" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="I837" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J837" s="6" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="K837" s="6" t="s">
         <v>29</v>
@@ -64626,16 +64650,16 @@
         <v>275</v>
       </c>
       <c r="R837" s="6" t="s">
+        <v>3750</v>
+      </c>
+      <c r="S837" s="6" t="s">
         <v>3751</v>
-      </c>
-      <c r="S837" s="6" t="s">
-        <v>3752</v>
       </c>
       <c r="T837" s="6" t="s">
         <v>251</v>
       </c>
       <c r="U837" s="7" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="838" spans="1:21" x14ac:dyDescent="0.2">
@@ -64648,10 +64672,10 @@
       </c>
       <c r="D838" s="5"/>
       <c r="E838" s="6" t="s">
+        <v>3753</v>
+      </c>
+      <c r="F838" s="6" t="s">
         <v>3754</v>
-      </c>
-      <c r="F838" s="6" t="s">
-        <v>3755</v>
       </c>
       <c r="G838" s="6" t="s">
         <v>25</v>
@@ -64709,10 +64733,10 @@
       </c>
       <c r="D839" s="5"/>
       <c r="E839" s="6" t="s">
+        <v>3755</v>
+      </c>
+      <c r="F839" s="6" t="s">
         <v>3756</v>
-      </c>
-      <c r="F839" s="6" t="s">
-        <v>3757</v>
       </c>
       <c r="G839" s="6" t="s">
         <v>25</v>
@@ -64770,10 +64794,10 @@
       </c>
       <c r="D840" s="5"/>
       <c r="E840" s="6" t="s">
+        <v>3757</v>
+      </c>
+      <c r="F840" s="6" t="s">
         <v>3758</v>
-      </c>
-      <c r="F840" s="6" t="s">
-        <v>3759</v>
       </c>
       <c r="G840" s="6" t="s">
         <v>25</v>
@@ -64831,22 +64855,22 @@
       </c>
       <c r="D841" s="5"/>
       <c r="E841" s="6" t="s">
+        <v>3759</v>
+      </c>
+      <c r="F841" s="6" t="s">
         <v>3760</v>
-      </c>
-      <c r="F841" s="6" t="s">
-        <v>3761</v>
       </c>
       <c r="G841" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H841" s="6" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="I841" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J841" s="6" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="K841" s="6" t="s">
         <v>449</v>
@@ -64892,10 +64916,10 @@
       </c>
       <c r="D842" s="5"/>
       <c r="E842" s="6" t="s">
+        <v>3763</v>
+      </c>
+      <c r="F842" s="6" t="s">
         <v>3764</v>
-      </c>
-      <c r="F842" s="6" t="s">
-        <v>3765</v>
       </c>
       <c r="G842" s="6" t="s">
         <v>25</v>
@@ -64953,10 +64977,10 @@
       </c>
       <c r="D843" s="5"/>
       <c r="E843" s="6" t="s">
+        <v>3765</v>
+      </c>
+      <c r="F843" s="6" t="s">
         <v>3766</v>
-      </c>
-      <c r="F843" s="6" t="s">
-        <v>3767</v>
       </c>
       <c r="G843" s="6" t="s">
         <v>25</v>
@@ -65010,14 +65034,14 @@
       </c>
       <c r="B844" s="5"/>
       <c r="C844" s="6" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="D844" s="5"/>
       <c r="E844" s="6" t="s">
+        <v>3768</v>
+      </c>
+      <c r="F844" s="6" t="s">
         <v>3769</v>
-      </c>
-      <c r="F844" s="6" t="s">
-        <v>3770</v>
       </c>
       <c r="G844" s="6" t="s">
         <v>25</v>
@@ -65053,16 +65077,16 @@
         <v>35</v>
       </c>
       <c r="R844" s="6" t="s">
+        <v>3770</v>
+      </c>
+      <c r="S844" s="6" t="s">
         <v>3771</v>
-      </c>
-      <c r="S844" s="6" t="s">
-        <v>3772</v>
       </c>
       <c r="T844" s="6" t="s">
         <v>2546</v>
       </c>
       <c r="U844" s="7" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="845" spans="1:21" x14ac:dyDescent="0.2">
@@ -65071,29 +65095,29 @@
       </c>
       <c r="B845" s="5"/>
       <c r="C845" s="6" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="D845" s="5"/>
       <c r="E845" s="6" t="s">
+        <v>3774</v>
+      </c>
+      <c r="F845" s="6" t="s">
         <v>3775</v>
-      </c>
-      <c r="F845" s="6" t="s">
-        <v>3776</v>
       </c>
       <c r="G845" s="6" t="s">
         <v>239</v>
       </c>
       <c r="H845" s="6" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="I845" s="6" t="s">
         <v>99</v>
       </c>
       <c r="J845" s="6" t="s">
+        <v>3777</v>
+      </c>
+      <c r="K845" s="6" t="s">
         <v>3778</v>
-      </c>
-      <c r="K845" s="6" t="s">
-        <v>3779</v>
       </c>
       <c r="L845" s="6" t="s">
         <v>63</v>
@@ -65123,7 +65147,7 @@
         <v>906</v>
       </c>
       <c r="U845" s="7" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="846" spans="1:21" x14ac:dyDescent="0.2">
@@ -65136,10 +65160,10 @@
       </c>
       <c r="D846" s="5"/>
       <c r="E846" s="6" t="s">
+        <v>3780</v>
+      </c>
+      <c r="F846" s="6" t="s">
         <v>3781</v>
-      </c>
-      <c r="F846" s="6" t="s">
-        <v>3782</v>
       </c>
       <c r="G846" s="6" t="s">
         <v>136</v>
@@ -65197,10 +65221,10 @@
       </c>
       <c r="D847" s="5"/>
       <c r="E847" s="6" t="s">
+        <v>3782</v>
+      </c>
+      <c r="F847" s="6" t="s">
         <v>3783</v>
-      </c>
-      <c r="F847" s="6" t="s">
-        <v>3784</v>
       </c>
       <c r="G847" s="6" t="s">
         <v>25</v>
@@ -65254,14 +65278,14 @@
       </c>
       <c r="B848" s="5"/>
       <c r="C848" s="6" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D848" s="5"/>
       <c r="E848" s="6" t="s">
+        <v>3785</v>
+      </c>
+      <c r="F848" s="6" t="s">
         <v>3786</v>
-      </c>
-      <c r="F848" s="6" t="s">
-        <v>3787</v>
       </c>
       <c r="G848" s="6" t="s">
         <v>25</v>
@@ -65276,7 +65300,7 @@
         <v>299</v>
       </c>
       <c r="K848" s="6" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="L848" s="6" t="s">
         <v>136</v>
@@ -65297,16 +65321,16 @@
         <v>275</v>
       </c>
       <c r="R848" s="6" t="s">
+        <v>3788</v>
+      </c>
+      <c r="S848" s="6" t="s">
         <v>3789</v>
       </c>
-      <c r="S848" s="6" t="s">
+      <c r="T848" s="6" t="s">
         <v>3790</v>
       </c>
-      <c r="T848" s="6" t="s">
+      <c r="U848" s="7" t="s">
         <v>3791</v>
-      </c>
-      <c r="U848" s="7" t="s">
-        <v>3792</v>
       </c>
     </row>
     <row r="849" spans="1:21" x14ac:dyDescent="0.2">
@@ -65315,26 +65339,26 @@
       </c>
       <c r="B849" s="5"/>
       <c r="C849" s="6" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D849" s="5"/>
       <c r="E849" s="6" t="s">
+        <v>3793</v>
+      </c>
+      <c r="F849" s="6" t="s">
         <v>3794</v>
-      </c>
-      <c r="F849" s="6" t="s">
-        <v>3795</v>
       </c>
       <c r="G849" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H849" s="6" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="I849" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J849" s="6" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="K849" s="6" t="s">
         <v>2288</v>
@@ -65358,16 +65382,16 @@
         <v>35</v>
       </c>
       <c r="R849" s="6" t="s">
+        <v>3797</v>
+      </c>
+      <c r="S849" s="6" t="s">
         <v>3798</v>
       </c>
-      <c r="S849" s="6" t="s">
+      <c r="T849" s="6" t="s">
         <v>3799</v>
       </c>
-      <c r="T849" s="6" t="s">
+      <c r="U849" s="7" t="s">
         <v>3800</v>
-      </c>
-      <c r="U849" s="7" t="s">
-        <v>3801</v>
       </c>
     </row>
     <row r="850" spans="1:21" x14ac:dyDescent="0.2">
@@ -65376,26 +65400,26 @@
       </c>
       <c r="B850" s="5"/>
       <c r="C850" s="6" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D850" s="5"/>
       <c r="E850" s="6" t="s">
+        <v>3802</v>
+      </c>
+      <c r="F850" s="6" t="s">
         <v>3803</v>
-      </c>
-      <c r="F850" s="6" t="s">
-        <v>3804</v>
       </c>
       <c r="G850" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H850" s="6" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="I850" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J850" s="6" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="K850" s="6" t="s">
         <v>29</v>
@@ -65419,81 +65443,142 @@
         <v>275</v>
       </c>
       <c r="R850" s="6" t="s">
+        <v>3750</v>
+      </c>
+      <c r="S850" s="6" t="s">
         <v>3751</v>
-      </c>
-      <c r="S850" s="6" t="s">
-        <v>3752</v>
       </c>
       <c r="T850" s="6" t="s">
         <v>2597</v>
       </c>
       <c r="U850" s="7" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="851" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A851" s="9">
+      <c r="A851" s="4">
         <v>850</v>
       </c>
-      <c r="B851" s="10"/>
-      <c r="C851" s="11" t="s">
+      <c r="B851" s="5"/>
+      <c r="C851" s="6" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D851" s="5"/>
+      <c r="E851" s="6" t="s">
         <v>3805</v>
       </c>
-      <c r="D851" s="10"/>
-      <c r="E851" s="11" t="s">
+      <c r="F851" s="6" t="s">
         <v>3806</v>
       </c>
-      <c r="F851" s="11" t="s">
+      <c r="G851" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H851" s="6" t="s">
         <v>3807</v>
       </c>
-      <c r="G851" s="11" t="s">
+      <c r="I851" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J851" s="6" t="s">
+        <v>3808</v>
+      </c>
+      <c r="K851" s="6" t="s">
+        <v>3809</v>
+      </c>
+      <c r="L851" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M851" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N851" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O851" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P851" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q851" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R851" s="6" t="s">
+        <v>3810</v>
+      </c>
+      <c r="S851" s="6" t="s">
+        <v>3811</v>
+      </c>
+      <c r="T851" s="6" t="s">
+        <v>3799</v>
+      </c>
+      <c r="U851" s="7" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="852" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A852" s="9">
+        <v>851</v>
+      </c>
+      <c r="B852" s="10"/>
+      <c r="C852" s="11" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D852" s="10"/>
+      <c r="E852" s="11" t="s">
+        <v>3814</v>
+      </c>
+      <c r="F852" s="11" t="s">
+        <v>3815</v>
+      </c>
+      <c r="G852" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H851" s="11" t="s">
-        <v>3808</v>
-      </c>
-      <c r="I851" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J851" s="11" t="s">
-        <v>3809</v>
-      </c>
-      <c r="K851" s="11" t="s">
-        <v>3810</v>
-      </c>
-      <c r="L851" s="11" t="s">
+      <c r="H852" s="11" t="s">
+        <v>3208</v>
+      </c>
+      <c r="I852" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J852" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="K852" s="11" t="s">
+        <v>3060</v>
+      </c>
+      <c r="L852" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="M851" s="11" t="s">
+      <c r="M852" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="N851" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O851" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P851" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q851" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R851" s="11" t="s">
-        <v>3811</v>
-      </c>
-      <c r="S851" s="11" t="s">
-        <v>3812</v>
-      </c>
-      <c r="T851" s="11" t="s">
-        <v>3800</v>
-      </c>
-      <c r="U851" s="12" t="s">
-        <v>3813</v>
+      <c r="N852" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O852" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P852" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q852" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R852" s="11" t="s">
+        <v>3137</v>
+      </c>
+      <c r="S852" s="11" t="s">
+        <v>3816</v>
+      </c>
+      <c r="T852" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U852" s="12" t="s">
+        <v>3817</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Dzhl23rTgykvy0kO6O1C6nLJNaL/lxCUY5BKfhiu70dC0nMpPpkFlxi8epj3CqpLqVKN+ZE/kDe5fFpY5HTHrA==" saltValue="SGkv3rW06GS2mHKNp0heyg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WJumHy/FOpcSnL1032aq585tvBXSHpQ9s8wsVznm5vPCGMqoZwHSdlEIE9JVknvLaD27Fot42/BwVLqZTQecQA==" saltValue="h7aTxNoDXeKM0wkTYhaOLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BF0C64-4C16-40B4-8882-AB076906FDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBE2199-F0EA-4322-980F-D3146E5612EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15835" uniqueCount="3820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15851" uniqueCount="3827">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11531,6 +11531,27 @@
   </si>
   <si>
     <t>Pet 120ml Round Green 25mm 12.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0453</t>
+  </si>
+  <si>
+    <t>MP0453.1</t>
+  </si>
+  <si>
+    <t>Measuring 38mm Taper Clear 25ml Cup</t>
+  </si>
+  <si>
+    <t>Taper</t>
+  </si>
+  <si>
+    <t>33.30 ± 0.30</t>
+  </si>
+  <si>
+    <t>4.40 ± 0.20</t>
+  </si>
+  <si>
+    <t>25.00</t>
   </si>
 </sst>
 </file>
@@ -12299,30 +12320,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{37E0A1A8-18AB-435A-8EA2-07384ABF1757}" name="Table1" displayName="Table1" ref="A1:U853" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U853" xr:uid="{37E0A1A8-18AB-435A-8EA2-07384ABF1757}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F155CB83-CEAB-4671-9CFD-CACC3480F29B}" name="Table1" displayName="Table1" ref="A1:U854" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U854" xr:uid="{F155CB83-CEAB-4671-9CFD-CACC3480F29B}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{A8A5CA21-9D9B-4A69-82CF-5670BBE1C4F6}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{18F82B40-077A-406D-ACA2-34E3108A8A1E}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{D773AADF-4D98-4FB5-B182-1565BBB4A13B}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{2D469E3C-9C5C-4A77-A9E0-B263CF2E3C8E}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{811FB727-3954-4B08-93B2-9122F0D8B168}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{81B60EDC-7AB9-4116-92EA-803C3F2EE48D}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{E1487E29-D932-41E8-928C-857813411778}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{4C5A81A1-27DF-49BC-9F24-231606B27897}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{288F7526-A613-4016-97BF-BD09A89BADFC}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{0182023F-807C-4D0F-AC35-6B1FBE521971}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{1604DB0F-BC21-4E8C-9E24-4EC9A9E39666}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{B71A96E2-1DA6-46D0-86E4-9DFABC33B648}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{5DF08D22-33D2-4F47-A155-040700D92FE8}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{0002B301-9790-4334-869D-DEB27874D3FC}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{E68AC660-108D-4AD9-A08E-D9EAD14F64A2}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{30FF466E-ACDA-40A7-8C33-503375DEA73D}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{B40FC791-BBBF-40D2-82B4-9E88C539F05C}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{DB721051-171B-4DFE-B196-B4E40235F76D}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{140BB9BD-6C71-4C9C-8901-3D5BAE841C25}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{F76C7FA9-3514-447C-973D-B77FB45BDAAB}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{2E5B29B4-9C66-4353-A512-C496127B62E6}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{6FBAA8A1-054C-4F96-B1B7-1775CE69D59A}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{34EA52EB-CE27-4BB2-A48B-0CCA1F3CE5A6}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C54D9D0E-F58D-4D99-9319-BE09414850D4}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{E3E3121E-2820-4CF8-B325-E41EBFDCDDEA}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{9DDBE99D-30A9-45E4-B2AF-55B346A86FF3}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{FE3C53C9-3A9F-4F22-91FC-240530A1A528}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{2A389947-2E57-46A1-83D4-BDAC37AC151F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{ABDF53FE-4851-43EC-B287-AA7ED9CC0B6F}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{2678B880-A136-45CB-B5D8-66DD8C451C21}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{79890D5D-A841-4881-A067-0959AE15D38A}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{CEACC636-9279-4990-BCF7-CFB8BE147332}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{6A3ACE4D-F0F1-462D-B954-FED3A678D19F}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{C58335F0-6BB6-4223-B007-9335CC85ABAD}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{AF7716B6-E99E-493F-B81F-001509DDC288}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{D394880A-6E19-4ACE-9B26-C7029706F087}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{8CBD40FA-E815-4E7D-BB0C-E74ADA57ED5E}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{A1B99600-DBCA-48F2-804F-5BD3840128F5}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{DDBED045-C778-46E2-AD32-03A383B8FD1C}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{1B09EE66-894F-4698-A4C4-5C0A43622789}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{31E7D2F1-B7E1-4E6D-B7E5-73463F89ECD1}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{E034F24A-2711-463D-BEBB-9C5FE5343B3F}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12625,7 +12646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U853"/>
+  <dimension ref="A1:U854"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -65584,68 +65605,125 @@
       </c>
     </row>
     <row r="853" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A853" s="9">
+      <c r="A853" s="4">
         <v>852</v>
       </c>
-      <c r="B853" s="10"/>
-      <c r="C853" s="11" t="s">
+      <c r="B853" s="5"/>
+      <c r="C853" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="D853" s="10"/>
-      <c r="E853" s="11" t="s">
+      <c r="D853" s="5"/>
+      <c r="E853" s="6" t="s">
         <v>3818</v>
       </c>
-      <c r="F853" s="11" t="s">
+      <c r="F853" s="6" t="s">
         <v>3819</v>
       </c>
-      <c r="G853" s="11" t="s">
+      <c r="G853" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H853" s="11" t="s">
+      <c r="H853" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="I853" s="11" t="s">
+      <c r="I853" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J853" s="11" t="s">
+      <c r="J853" s="6" t="s">
         <v>814</v>
       </c>
-      <c r="K853" s="11" t="s">
+      <c r="K853" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L853" s="11" t="s">
+      <c r="L853" s="6" t="s">
         <v>815</v>
       </c>
-      <c r="M853" s="11" t="s">
+      <c r="M853" s="6" t="s">
         <v>816</v>
       </c>
-      <c r="N853" s="11" t="s">
+      <c r="N853" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="O853" s="11" t="s">
+      <c r="O853" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="P853" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q853" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R853" s="11" t="s">
+      <c r="P853" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q853" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R853" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="S853" s="11" t="s">
+      <c r="S853" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="T853" s="11" t="s">
+      <c r="T853" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="U853" s="12" t="s">
+      <c r="U853" s="7" t="s">
         <v>819</v>
       </c>
     </row>
+    <row r="854" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A854" s="9">
+        <v>853</v>
+      </c>
+      <c r="B854" s="10"/>
+      <c r="C854" s="11" t="s">
+        <v>3820</v>
+      </c>
+      <c r="D854" s="10"/>
+      <c r="E854" s="11" t="s">
+        <v>3821</v>
+      </c>
+      <c r="F854" s="11" t="s">
+        <v>3822</v>
+      </c>
+      <c r="G854" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H854" s="11" t="s">
+        <v>1802</v>
+      </c>
+      <c r="I854" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="J854" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K854" s="11" t="s">
+        <v>3823</v>
+      </c>
+      <c r="L854" s="10"/>
+      <c r="M854" s="10"/>
+      <c r="N854" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="O854" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="P854" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q854" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R854" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="S854" s="11" t="s">
+        <v>3824</v>
+      </c>
+      <c r="T854" s="11" t="s">
+        <v>3825</v>
+      </c>
+      <c r="U854" s="12" t="s">
+        <v>3826</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XWr3e3OCjhw/cNU9yoEnc9Jl0ibl1gV3wRkP8DAHxeS9xVFHMGxvReRuHvlrAT/bk2TtuwnsN1pPEeMFcLmJFg==" saltValue="L7sAqzD7Sg9Yg9weUQtCaw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sw51ZsQ4oWdMAIeW2kZw85sFgRY19FZ6poXiR6N29ne+0acqvcv8Biwc/+RCekW95tOB/Z6z4JlftYcIDDcjKQ==" saltValue="WpSjoPXyU5uOSNv1e7EyRg==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
